--- a/artfynd/A 31468-2025 artfynd.xlsx
+++ b/artfynd/A 31468-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,6 +1038,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126414507</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Häcklarens mo, Häcklarens mo, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559537</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6509635</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31468-2025 artfynd.xlsx
+++ b/artfynd/A 31468-2025 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>126414507</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31468-2025 artfynd.xlsx
+++ b/artfynd/A 31468-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97570958</v>
+        <v>126414507</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klintaberget/Skybygget, Ög</t>
+          <t>Häcklarens mo, Häcklarens mo, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559670.7677368862</v>
+        <v>559537</v>
       </c>
       <c r="R2" t="n">
-        <v>6509656.307680644</v>
+        <v>6509635</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,78 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124627772</v>
+        <v>92005771</v>
       </c>
       <c r="B3" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ämtetorp SV 1010 m, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559523</v>
+        <v>559712</v>
       </c>
       <c r="R3" t="n">
-        <v>6509609</v>
+        <v>6509547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,90 +859,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124628173</v>
+        <v>97570954</v>
       </c>
       <c r="B4" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ämtetorp SV 945 m, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559561</v>
+        <v>559588</v>
       </c>
       <c r="R4" t="n">
-        <v>6509661</v>
+        <v>6509779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,12 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,34 +965,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126414507</v>
+        <v>97570958</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,37 +994,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häcklarens mo, Häcklarens mo, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559537</v>
+        <v>559671</v>
       </c>
       <c r="R5" t="n">
-        <v>6509635</v>
+        <v>6509657</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,12 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,15 +1073,355 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124627772</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ämtetorp SV 1010 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559523</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6509609</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124628173</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ämtetorp SV 945 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559561</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6509661</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80180469</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Valborgsmässoberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559555</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6509837</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Axel Lindahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Axel Lindahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31468-2025 artfynd.xlsx
+++ b/artfynd/A 31468-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126414507</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005771</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97570954</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97570958</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628173</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,8 +1457,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80180469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>